--- a/data/trans_orig/P5_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P5_R-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15842</t>
+          <t>16291</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28870</t>
+          <t>29078</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13706</t>
+          <t>13520</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24990</t>
+          <t>25274</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33111</t>
+          <t>32470</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>50618</t>
+          <t>49795</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>32,74%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51585</t>
+          <t>51377</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>64613</t>
+          <t>64164</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>46647</t>
+          <t>46363</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57931</t>
+          <t>58117</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>101474</t>
+          <t>102297</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>118981</t>
+          <t>119622</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,65%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7837</t>
+          <t>7594</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18260</t>
+          <t>18454</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9093</t>
+          <t>8888</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19807</t>
+          <t>20117</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19602</t>
+          <t>19341</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33897</t>
+          <t>34087</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>25,03%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>50427</t>
+          <t>50233</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>60850</t>
+          <t>61093</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>47678</t>
+          <t>47368</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>58392</t>
+          <t>58597</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>70,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>102275</t>
+          <t>102085</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>116570</t>
+          <t>116831</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,8%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7202</t>
+          <t>7182</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16888</t>
+          <t>17342</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18740</t>
+          <t>18837</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32034</t>
+          <t>32581</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28576</t>
+          <t>29682</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45662</t>
+          <t>46344</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,59%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>41357</t>
+          <t>40903</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51043</t>
+          <t>51063</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>51910</t>
+          <t>51363</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>65204</t>
+          <t>65107</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>96527</t>
+          <t>95845</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>113613</t>
+          <t>112507</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,89%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>79,12%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>40119</t>
+          <t>40742</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>59533</t>
+          <t>58503</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32848</t>
+          <t>32642</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49852</t>
+          <t>49540</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>76024</t>
+          <t>77208</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>102113</t>
+          <t>101824</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>33,96%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>91763</t>
+          <t>92793</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>111177</t>
+          <t>110554</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>98710</t>
+          <t>99022</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>115714</t>
+          <t>115920</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>197745</t>
+          <t>198034</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>223834</t>
+          <t>222650</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>74,25%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16334</t>
+          <t>17049</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>28442</t>
+          <t>29962</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21832</t>
+          <t>22291</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35450</t>
+          <t>36045</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>42029</t>
+          <t>42541</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61272</t>
+          <t>61199</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>39,83%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40681</t>
+          <t>39161</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>52074</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>49080</t>
+          <t>48485</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>62698</t>
+          <t>62239</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>92380</t>
+          <t>92453</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>111623</t>
+          <t>111111</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,31%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16964</t>
+          <t>17812</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30576</t>
+          <t>30300</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14337</t>
+          <t>14569</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26127</t>
+          <t>26817</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>35237</t>
+          <t>34933</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>52672</t>
+          <t>52771</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,83%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>44294</t>
+          <t>44570</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>57906</t>
+          <t>57058</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,34%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>46265</t>
+          <t>45575</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>58055</t>
+          <t>57823</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>94590</t>
+          <t>94491</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>112025</t>
+          <t>112329</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>76,28%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>124058</t>
+          <t>124621</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>157946</t>
+          <t>155811</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>130804</t>
+          <t>132896</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>162956</t>
+          <t>166042</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>264699</t>
+          <t>266221</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>312169</t>
+          <t>312573</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,31%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>344729</t>
+          <t>346864</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>378617</t>
+          <t>378054</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>365593</t>
+          <t>362507</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>397745</t>
+          <t>395653</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>68,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>719056</t>
+          <t>718652</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>766526</t>
+          <t>765004</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>69,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>74,18%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17111</t>
+          <t>17074</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29698</t>
+          <t>29395</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24608</t>
+          <t>24430</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38271</t>
+          <t>38194</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45468</t>
+          <t>44552</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>64277</t>
+          <t>64263</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>47,73%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31523</t>
+          <t>31826</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44110</t>
+          <t>44147</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35139</t>
+          <t>35216</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48802</t>
+          <t>48980</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>66,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>70354</t>
+          <t>70368</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>89163</t>
+          <t>90079</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>52,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>66,91%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17829</t>
+          <t>17375</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30821</t>
+          <t>30515</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>46,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24411</t>
+          <t>24636</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37301</t>
+          <t>37851</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45835</t>
+          <t>45391</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>65115</t>
+          <t>65313</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>48,78%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>34558</t>
+          <t>34864</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>47550</t>
+          <t>48004</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,86%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>31225</t>
+          <t>30675</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>44115</t>
+          <t>43890</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>64,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>68790</t>
+          <t>68592</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>88070</t>
+          <t>88514</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>66,1%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14672</t>
+          <t>15308</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27583</t>
+          <t>27873</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17075</t>
+          <t>17374</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29972</t>
+          <t>30658</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>35724</t>
+          <t>35659</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>53427</t>
+          <t>53225</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,58%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38940</t>
+          <t>38650</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51851</t>
+          <t>51215</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>37992</t>
+          <t>37306</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50889</t>
+          <t>50590</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>54,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>74,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>81060</t>
+          <t>81262</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>98763</t>
+          <t>98828</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>73,49%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51214</t>
+          <t>50847</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>70204</t>
+          <t>69883</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45702</t>
+          <t>45297</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64942</t>
+          <t>65636</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>103061</t>
+          <t>103092</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>131021</t>
+          <t>130123</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>43,99%</t>
+          <t>43,69%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>66276</t>
+          <t>66597</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>85266</t>
+          <t>85633</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>96422</t>
+          <t>95728</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>115662</t>
+          <t>116067</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>166823</t>
+          <t>167721</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>194783</t>
+          <t>194752</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>56,01%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>65,39%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21109</t>
+          <t>20820</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36795</t>
+          <t>36401</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25058</t>
+          <t>24998</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41409</t>
+          <t>40204</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>50000</t>
+          <t>50672</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>71647</t>
+          <t>71308</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>38,45%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>56656</t>
+          <t>57050</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>72342</t>
+          <t>72631</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>61,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>50599</t>
+          <t>51804</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>66950</t>
+          <t>67010</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>113812</t>
+          <t>114151</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>135459</t>
+          <t>134787</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>72,68%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18963</t>
+          <t>18705</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31041</t>
+          <t>31158</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>25969</t>
+          <t>25274</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>39450</t>
+          <t>39783</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>48081</t>
+          <t>47528</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>66421</t>
+          <t>66363</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>51,87%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22870</t>
+          <t>22753</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>34948</t>
+          <t>35206</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34588</t>
+          <t>34255</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>48069</t>
+          <t>48764</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>64,92%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>61528</t>
+          <t>61586</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>79868</t>
+          <t>80421</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>62,85%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>165150</t>
+          <t>164635</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>199619</t>
+          <t>199800</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>187751</t>
+          <t>187232</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>224557</t>
+          <t>224232</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>363027</t>
+          <t>361476</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>412614</t>
+          <t>414824</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,9%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>277346</t>
+          <t>277165</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>311815</t>
+          <t>312330</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>312753</t>
+          <t>313078</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>349559</t>
+          <t>350078</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>65,06%</t>
+          <t>65,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>601661</t>
+          <t>599451</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>651248</t>
+          <t>652799</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>64,36%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20153</t>
+          <t>19661</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32333</t>
+          <t>32679</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>50,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23829</t>
+          <t>23435</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37869</t>
+          <t>37444</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>47,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>46988</t>
+          <t>45928</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>66111</t>
+          <t>65567</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>45,82%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32498</t>
+          <t>32152</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44678</t>
+          <t>45170</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>69,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40385</t>
+          <t>40810</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>54425</t>
+          <t>54819</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,55%</t>
+          <t>70,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>76974</t>
+          <t>77518</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>96097</t>
+          <t>97157</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>67,9%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22251</t>
+          <t>22183</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36363</t>
+          <t>36161</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24347</t>
+          <t>24608</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38833</t>
+          <t>39152</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>50043</t>
+          <t>51114</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>71336</t>
+          <t>70599</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>40,26%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>45948</t>
+          <t>46150</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>60060</t>
+          <t>60128</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>73,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>54234</t>
+          <t>53915</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>68720</t>
+          <t>68459</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>73,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>104042</t>
+          <t>104779</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>125335</t>
+          <t>124264</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>70,85%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11298</t>
+          <t>11700</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22756</t>
+          <t>22235</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15537</t>
+          <t>15489</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26994</t>
+          <t>27284</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29855</t>
+          <t>30246</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44926</t>
+          <t>45841</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>41,59%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26468</t>
+          <t>26989</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37926</t>
+          <t>37524</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>54,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34017</t>
+          <t>33727</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>45474</t>
+          <t>45522</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>55,76%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>65308</t>
+          <t>64393</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>80379</t>
+          <t>79988</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,25%</t>
+          <t>58,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>72,56%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43933</t>
+          <t>43537</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63897</t>
+          <t>63780</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56040</t>
+          <t>54859</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75564</t>
+          <t>76223</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>104204</t>
+          <t>104834</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>133108</t>
+          <t>134019</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,81%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>101900</t>
+          <t>102017</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>121864</t>
+          <t>122260</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>95319</t>
+          <t>94660</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>114843</t>
+          <t>116024</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>55,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,21%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>203572</t>
+          <t>202661</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>232476</t>
+          <t>231846</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,05%</t>
+          <t>68,86%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26272</t>
+          <t>26155</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41625</t>
+          <t>41677</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>30696</t>
+          <t>30421</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>46774</t>
+          <t>45536</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>60922</t>
+          <t>61223</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>84316</t>
+          <t>84950</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>42,32%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>59954</t>
+          <t>59902</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>75307</t>
+          <t>75424</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>52379</t>
+          <t>53617</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>68457</t>
+          <t>68732</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,04%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>116416</t>
+          <t>115782</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>139810</t>
+          <t>139509</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>57,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>69,5%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17539</t>
+          <t>16940</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29347</t>
+          <t>30199</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20263</t>
+          <t>20046</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>33566</t>
+          <t>33680</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>41368</t>
+          <t>40368</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>59603</t>
+          <t>58282</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>45,89%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>29820</t>
+          <t>28968</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>41628</t>
+          <t>42227</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>48,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34259</t>
+          <t>34145</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>47562</t>
+          <t>47779</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>67388</t>
+          <t>68709</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>85623</t>
+          <t>86623</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>68,21%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>165047</t>
+          <t>164518</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>198858</t>
+          <t>199461</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>195603</t>
+          <t>192946</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>232052</t>
+          <t>231250</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>367665</t>
+          <t>369547</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>421624</t>
+          <t>420621</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,48%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>324050</t>
+          <t>323447</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>357861</t>
+          <t>358390</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>338140</t>
+          <t>338942</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>374589</t>
+          <t>377246</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>671477</t>
+          <t>672480</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>725436</t>
+          <t>723554</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>66,19%</t>
         </is>
       </c>
     </row>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13938</t>
+          <t>14283</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27528</t>
+          <t>26908</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16684</t>
+          <t>16284</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33625</t>
+          <t>32994</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34659</t>
+          <t>35065</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56351</t>
+          <t>55816</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,22%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76934</t>
+          <t>77554</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>90524</t>
+          <t>90179</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>74,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>102340</t>
+          <t>102971</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>119281</t>
+          <t>119681</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>184075</t>
+          <t>184610</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>205767</t>
+          <t>205361</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,42%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10969</t>
+          <t>11275</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23765</t>
+          <t>23699</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9193</t>
+          <t>10171</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23211</t>
+          <t>22680</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24866</t>
+          <t>25222</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>42405</t>
+          <t>43052</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,63%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>70916</t>
+          <t>70982</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>83712</t>
+          <t>83406</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>74,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>72362</t>
+          <t>72893</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>86380</t>
+          <t>85402</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>147849</t>
+          <t>147202</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>165388</t>
+          <t>165032</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,74%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6244</t>
+          <t>5906</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16093</t>
+          <t>15861</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3703</t>
+          <t>3575</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12913</t>
+          <t>12571</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11757</t>
+          <t>11730</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25355</t>
+          <t>24847</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,47%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35768</t>
+          <t>36000</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45617</t>
+          <t>45955</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50940</t>
+          <t>51282</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>60150</t>
+          <t>60278</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>90359</t>
+          <t>90867</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>103957</t>
+          <t>103984</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>78,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,86%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29068</t>
+          <t>29403</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>105071</t>
+          <t>113523</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31256</t>
+          <t>30693</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52713</t>
+          <t>52227</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>69640</t>
+          <t>67797</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>181059</t>
+          <t>157792</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>36,22%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>112337</t>
+          <t>103885</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>188340</t>
+          <t>188005</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>165559</t>
+          <t>166045</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>187016</t>
+          <t>187579</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>254621</t>
+          <t>277888</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>366040</t>
+          <t>367883</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>84,44%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22072</t>
+          <t>22697</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38394</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18733</t>
+          <t>19310</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36789</t>
+          <t>37159</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45444</t>
+          <t>44058</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>68972</t>
+          <t>70560</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>25,02%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>81311</t>
+          <t>81034</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>97356</t>
+          <t>96731</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>125828</t>
+          <t>125458</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>143884</t>
+          <t>143307</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>213073</t>
+          <t>211485</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>236601</t>
+          <t>237987</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>84,38%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4493</t>
+          <t>4690</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13728</t>
+          <t>14257</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8325</t>
+          <t>8541</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20112</t>
+          <t>20370</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15062</t>
+          <t>14649</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30407</t>
+          <t>29425</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>20,88%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>55167</t>
+          <t>54638</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>64402</t>
+          <t>64205</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>51891</t>
+          <t>51633</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>63678</t>
+          <t>63462</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>110491</t>
+          <t>111473</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>125836</t>
+          <t>126249</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,6%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>113120</t>
+          <t>113470</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>223862</t>
+          <t>221006</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>108990</t>
+          <t>109849</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>148128</t>
+          <t>148481</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>235970</t>
+          <t>236316</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>354353</t>
+          <t>357352</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,43%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>432874</t>
+          <t>435730</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>543616</t>
+          <t>543266</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>600154</t>
+          <t>599801</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>639292</t>
+          <t>638433</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1050665</t>
+          <t>1047666</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1169048</t>
+          <t>1168702</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,18%</t>
         </is>
       </c>
     </row>
